--- a/public/filesDownload/myCabas_model_import.xlsx
+++ b/public/filesDownload/myCabas_model_import.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07873E37-1932-4384-8222-F7ADB8257E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10000" windowHeight="20000" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Produits" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Catégories" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Unités" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Instructions" state="visible" r:id="rId7"/>
+    <sheet name="Produits" sheetId="1" r:id="rId1"/>
+    <sheet name="Catégories" sheetId="2" r:id="rId2"/>
+    <sheet name="Unités" sheetId="3" r:id="rId3"/>
+    <sheet name="Instructions" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
   <si>
     <t>Nom *</t>
   </si>
@@ -34,9 +46,6 @@
     <t>Unité *</t>
   </si>
   <si>
-    <t>MOQ *</t>
-  </si>
-  <si>
     <t>Bio</t>
   </si>
   <si>
@@ -266,36 +275,53 @@
   </si>
   <si>
     <t>Après l'import, ajustez les prix et stocks par marché depuis votre tableau de bord.</t>
+  </si>
+  <si>
+    <t>Prix par pièce</t>
+  </si>
+  <si>
+    <t>Poids approximatif par pièce</t>
+  </si>
+  <si>
+    <t>Vente à la pièce possible *</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF9CA3AF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF9CA3AF"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -342,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -351,6 +377,14 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,18 +723,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,129 +748,161 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="7">
         <v>4.5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="2">
+        <f>IF(E2="","",G2/E2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H4" si="0">IF(E3="","",G3/E3)</f>
+        <v>0.171875</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>12</v>
+      <c r="J4" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="error" errorTitle="Catégorie invalide" error="Veuillez sélectionner une catégorie dans la liste déroulante." sqref="C2:C500">
-      <formula1>'Catégories'!$A$2:$A$9</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" showErrorMessage="1" errorStyle="error" errorTitle="Prix invalide" error="Le prix doit être un nombre positif supérieur à 0 (ex: 4.50)." sqref="D2:D500">
+  <dataValidations count="5">
+    <dataValidation type="decimal" operator="greaterThan" showErrorMessage="1" errorTitle="Prix invalide" error="Le prix doit être un nombre positif supérieur à 0 (ex: 4.50)." sqref="E2:E500" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="error" errorTitle="Unité invalide" error="Unités acceptées : kg, g, pièce, botte, litre, cl, barquette, pot, sachet, bouteille" sqref="E2:E500">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Unité invalide" error="Unités acceptées : kg, g, pièce, botte, litre, cl, barquette, pot, sachet, bouteille" sqref="D2:D500" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"kg,g,pièce,botte,litre,cl,barquette,pot,sachet,bouteille"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="MOQ invalide" error="La quantité minimum doit être un nombre positif (ex: 0.5, 1, 2). Laissez vide pour 1 par défaut." sqref="F2:F500">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="MOQ invalide" error="La quantité minimum doit être un nombre positif (ex: 0.5, 1, 2). Laissez vide pour 1 par défaut." sqref="G2:G500" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Valeur invalide" error="Sélectionnez &quot;Oui&quot; ou &quot;Non&quot; dans la liste déroulante." sqref="G2:G500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valeur invalide" error="Sélectionnez &quot;Oui&quot; ou &quot;Non&quot; dans la liste déroulante." sqref="I2:J500" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Valeur invalide" error="Sélectionnez &quot;Oui&quot; ou &quot;Non&quot; dans la liste déroulante." sqref="H2:H500">
+    <dataValidation type="list" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="MOQ invalide" error="La quantité minimum doit être un nombre positif (ex: 0.5, 1, 2). Laissez vide pour 1 par défaut." sqref="F2:F1048576" xr:uid="{586255DC-101F-44C7-A241-3DDC8009FED8}">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Catégorie invalide" error="Veuillez sélectionner une catégorie dans la liste déroulante." xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Catégories!$A$2:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:D500</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -841,7 +910,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -849,78 +918,78 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -928,288 +997,288 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
         <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A36"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>